--- a/forms/trg/Formulir_TRG_adaptivepublic-orga.xlsx
+++ b/forms/trg/Formulir_TRG_adaptivepublic-orga.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Nuralamsyah Ismail, S.Sos., M.A.</t>
+          <t>Prof. Dr. Gita Susanti, M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Public Organization</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -950,12 +946,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Irma Ariyanti Arif, S.Sos., M.Si</t>
+          <t>Nuralamsyah Ismail, S.Sos., M.A.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +961,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Public Organization, Communnity Development</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ishak Salim, S.IP., M.A</t>
+          <t>Irma Ariyanti Arif, S.Sos., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Public Organization, Communnity Development</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andi Ahmad Yani, S.Sos, M.Si, MPA, M.Sc</t>
+          <t>Dr. Ishak Salim, S.IP., M.A</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Public Governance</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,12 +1057,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Alwi, M.Si</t>
+          <t>Andi Ahmad Yani, S.Sos, M.Si, MPA, M.Sc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Public Governance</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1103,7 +1099,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1135,12 +1131,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Andi Ahmad Yani, S.Sos, M.Si, MPA, M.Sc</t>
+          <t>Prof. Dr. Alwi, M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1150,7 +1146,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Public Governance</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,12 +1168,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ishak Salim, S.IP., M.A</t>
+          <t>Andi Ahmad Yani, S.Sos, M.Si, MPA, M.Sc</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1187,7 +1183,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Public Governance</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,12 +1205,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Irma Ariyanti Arif, S.Sos., M.Si</t>
+          <t>Dr. Ishak Salim, S.IP., M.A</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1224,7 +1220,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Public Organization, Communnity Development</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,12 +1242,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Nuralamsyah Ismail, S.Sos., M.A.</t>
+          <t>Irma Ariyanti Arif, S.Sos., M.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1261,7 +1257,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Public Organization, Communnity Development</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,22 +1279,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Asiyah Kassim</t>
+          <t>Nuralamsyah Ismail, S.Sos., M.A.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi Mara (UiTM) Malaysia</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Public Management</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1320,16 +1316,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Sri Nurindah Sari Arsyad, S.Sos., M.A.P</t>
+          <t>Dr. Asiyah Kassim</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Universiti Teknologi Mara (UiTM) Malaysia</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Public Management</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1349,12 +1353,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Regina Sapta Samudera, S.A.P., M.A.P</t>
+          <t>Sri Nurindah Sari Arsyad, S.Sos., M.A.P</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1378,19 +1382,15 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Adriana M</t>
+          <t>Regina Sapta Samudera, S.A.P., M.A.P</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
@@ -1411,15 +1411,19 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Sulfira</t>
+          <t>Adriana M</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
@@ -1438,10 +1442,22 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Sulfira</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Our research focuses on assessing the capacities of public organizations in responding to crises, integrating cultural and social dimensions into resilience strategies, and developing governance models that enhance disaster preparedness and recovery.</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1449,7 +1465,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1638,15 +1658,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
